--- a/VerveStacks_MEX_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_MEX_grids_kan/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16B6CE04-469B-4B40-8015-081976759099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C52027FA-FD87-4113-BADF-01EA8473288D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3353,7 +3353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C9D2D8-5822-418A-8188-68FEC547500A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812E1E4F-161B-4FC0-BAB5-BB1FB4D5F5F1}">
   <dimension ref="B9:E371"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_MEX_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_MEX_grids_kan/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C52027FA-FD87-4113-BADF-01EA8473288D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F67AB3D-EB5E-4FF8-B88A-392B96930280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3353,7 +3353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812E1E4F-161B-4FC0-BAB5-BB1FB4D5F5F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3623E7C9-3891-4AD5-892E-FF50288E9A7C}">
   <dimension ref="B9:E371"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
